--- a/Result/checksun_type/其他配件.xlsx
+++ b/Result/checksun_type/其他配件.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>138.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>144.7</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>158.31</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>158.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>126140252.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>179646773.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>179646773.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>288541776.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>249860076.6</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>249860076.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-13008524.13905758</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>126140252</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>126140252.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>135.6</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>145.35</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>158.83</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>145.35</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>158.83</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>149355643.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>199168061.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>199168061</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>286806442.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>252995092.08</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>252995092.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-5288395.852468729</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>149355643</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>149355643.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>133.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>146.28</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>159.48</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>146.28</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>159.48</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>236429825.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>243968869.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>243968869</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>280669574.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>255272113.08</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>255272113.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>3441866.801674962</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>236429825</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>236429825.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>132.9</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>147.28</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>160.17</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>147.28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>160.17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>173429988.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>305348589.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>305348589</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>272591978.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>254388028.92</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>254388028.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>6461370.136106104</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>173429988</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>173429988.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>133.4</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>148.32</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>160.95</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>148.32</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>160.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>212878160.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>421450515.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>421450515</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>274650710.4</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>254522728.7</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>254522728.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>17294165.64471823</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>212878160</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>212878160.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>136.3</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>149.6</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>161.73</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>149.6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>161.73</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>223746689.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>397436778.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>397436778.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>263301806.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>254911229.58</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>254911229.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>27925349.16970986</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>223746689</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>223746689.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>140.1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>151.12</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>162.59</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>151.12</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>162.59</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>373359683.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>374444824.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>374444824.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>252575891.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>255257682.72</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>255257682.72</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>40950935.056494</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>373359683</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>373359683.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>143.9</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>152.65</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>163.44</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>152.65</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>163.44</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>543328425.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>317370279.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>317370279</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>231842549.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>254515985.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>254515985.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>42066417.85702515</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>543328425</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>543328425.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>147.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>154.25</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>164.29</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>154.25</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>164.29</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>753939618.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>239835367.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>239835367</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>202283159.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>250790390.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>250790390.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>23946656.00574735</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>753939618</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>753939618.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>149.6</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>155.78</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>165.1</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>155.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>165.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>92809478.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>127850905.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>127850905.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>148995940.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>248204610.78</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>248204610.78</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-25359440.74628332</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>92809478</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>92809478.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>150.2</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>156.57</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>165.78</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>156.57</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>165.78</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>108786918.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>129166834.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>129166834.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>167987433.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>261232164.76</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>261232164.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-24055655.36538848</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>108786918</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>108786918.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>31.99</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>31.38</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>31.62</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>31.62</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>436235108.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>163075735.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>163075735</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>120542346.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>106027794.62</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>106027794.62</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>23813420.93522564</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>436235108</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>436235108.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>31.4</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>31.27</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>31.61</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>74194978.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>90018253.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>90018253.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>85751812.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>101483765.1</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>101483765.1</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1753824.401134402</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>74194978</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>74194978.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>31.1</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>31.63</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>31.63</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>160381912.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>98740967.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>98740967.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>92145190.8</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>104398068.18</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>104398068.18</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>574189.9183917642</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>160381912</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>30.85</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>31.21</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>31.66</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>92683555.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>82943757.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>82943757.40000001</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>93041524.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>110958961.04</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>110958961.04</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-5354896.479370564</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>92683555</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>92683555.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>30.83</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>31.2</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>31.73</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>31.73</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>51883122.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>76714098.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>76714098.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>116606296.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>127513369.12</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>127513369.12</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-6380378.209053501</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>51883122</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>51883122.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>30.95</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>31.23</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>31.77</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>31.77</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>70947702.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>78008957.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>78008957.40000001</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>135866087.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>132601320.34</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>132601320.34</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-3246006.493991509</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>70947702</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>70947702.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>31.21</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>31.26</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>31.8</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>117808545.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>81485371.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>81485371</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>134782845.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>133719606.02</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>133719606.02</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-695037.3834032714</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>117808545</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>117808545.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>31.38</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>31.28</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>31.82</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>31.82</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>81395863.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>85549414.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>85549414.40000001</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>131413112.1</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>134538953.8</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>134538953.8</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-2046777.640298501</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>81395863</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>81395863.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>31.76</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>31.3</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>31.85</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>61535262.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>103139291.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>103139291</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>128774154.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>137249141.86</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>137249141.86</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-3377.162995308638</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>61535262</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>61535262.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>31.96</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>31.3</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>31.87</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>31.87</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>58357415.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>156498494.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>156498494.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>129085113.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>141953833.54</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>141953833.54</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>5043808.524687648</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>58357415</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>58357415.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>32.1</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>31.26</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>31.85</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>88329770.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>193723218.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>193723218.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>128668962.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>147438804.66</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>147438804.66</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>12414421.38121018</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>88329770</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>88329770.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>25.82</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>25.42</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>25.42</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>1436224.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1424472.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1424472.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>2096104.2</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>2996235.98</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>2996235.98</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-217468.8723230569</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>1436224</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>1436224.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>25.7</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>25.36</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>25.36</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>439725.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1385394.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1385394.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>2453313.7</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>2992311.72</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>2992311.72</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-208762.9886508698</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>439725</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>439725.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>25.64</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>25.38</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>25.31</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>25.31</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1501799.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>2136472.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>2136472.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>3128002.2</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>3005349.36</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>3005349.36</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-82102.44095307123</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1501799</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1501799.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>25.75</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>25.34</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>25.26</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>25.26</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>2047963.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>2423759.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>2423759</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>3007961.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>2993427.38</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>2993427.38</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-12020.21420789231</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>2047963</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>2047963.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>25.89</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>25.32</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>25.21</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>25.21</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1696650.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>2674372.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>2674372.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>2900423.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>2969257.8</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>2969257.8</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>30008.97450693091</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1696650</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1696650.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>25.97</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>25.3</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>25.16</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>25.16</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1240836.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>2767736.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>2767736.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>2870007.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>2951610.74</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>2951610.74</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>126619.6021528593</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1240836</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1240836.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>26.11</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>25.29</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>25.11</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>25.11</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>4195114.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>3521232.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>3521232.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>2815478.9</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>2934653.98</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>2934653.98</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>308949.8701415835</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>4195114</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>4195114.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>26.21</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>25.06</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>2938232.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>4119532.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>4119532</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>2513925.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2871310.36</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2871310.36</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>241857.971906133</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>2938232</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>2938232.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>25.93</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>25.01</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>25.01</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>3301032.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>3592164.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>3592164.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>2382852.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2887365.38</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2887365.38</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>272040.5468588425</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>3301032</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>3301032.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>25.64</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>24.95</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>24.95</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>2163467.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>3126473.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>3126473.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>2282476.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2847130.04</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>2847130.04</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>266571.3486891831</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>2163467</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>2163467.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>25.35</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>25.11</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>24.88</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>24.88</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>5008319.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>2972279.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>2972279.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>2167880.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>2819112.62</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>2819112.62</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>371119.7674221992</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>5008319</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>5008319.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>212.2</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>215.15</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>222.71</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>215.15</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>222.71</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>372575774.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>370448710.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>370448710</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>356963397.6</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>340102607.36</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>340102607.36</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>12835252.70437455</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>372575774</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>372575774.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>209.3</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>215.0</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>222.64</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>215</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>222.64</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>250038319.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>418803335.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>418803335.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>329523207.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>338508963.76</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>338508963.76</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>13167888.57472128</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>250038319</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>250038319.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>208.0</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>215.02</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>222.81</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>215.02</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>222.81</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>441008305.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>471411969.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>471411969.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>320004800.2</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>339175124.02</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>339175124.02</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>26301813.9761194</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>441008305</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>441008305.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>208.7</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>215.32</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>223.01</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>215.32</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>223.01</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>422128853.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>428949255.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>428949255.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>292285522.0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>335033438.96</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>335033438.96</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>23664144.12182677</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>422128853</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>422128853.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>210.1</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>216.6</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>223.27</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>223.27</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>366492299.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>392354750.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>392354750.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>289774229.7</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>330229814.24</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>330229814.24</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>21073694.75420058</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>366492299</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>366492299.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>211.9</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>217.68</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>223.37</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>217.68</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>223.37</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>614348902.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>343478085.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>343478085.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>282898236.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>325710502.3</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>325710502.3</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>22581480.20208466</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>614348902</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>614348902.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>214.4</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>218.9</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>223.56</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>223.56</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>513081489.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>240243078.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>240243078.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>248857041.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>321629937.86</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>321629937.86</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-2627086.629583895</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>513081489</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>513081489.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>216.5</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>219.88</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>223.83</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>219.88</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>223.83</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>228694736.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>168597630.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>168597630.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>221270619.2</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>315268561.34</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>315268561.34</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-27695420.47376823</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>228694736</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>228694736.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>217.6</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>220.45</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>224.01</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>220.45</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>224.01</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>239156326.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>155621788.2</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>155621788.2</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>244913618.7</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>314070486.46</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>314070486.46</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-32048194.55568263</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>239156326</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>239156326.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>219.8</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>221.05</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>224.18</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>221.05</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>224.18</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>122108973.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>187193709.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>187193709</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>250922645.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>316125773.38</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>316125773.38</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-38242749.51000029</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>122108973</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>122108973.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>220.0</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>221.05</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>224.43</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>221.05</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>224.43</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>98173870.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>222318388.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>222318388.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>284437268.2</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>316292792.6</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>316292792.6</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-33185513.4265255</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>98173870</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>98173870.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>37.47</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>38.08</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>40.03</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>40.03</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>35810040.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>75499582.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>75499582.59999999</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>55792550.2</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>33454972.78</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>33454972.78</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>7886638.29228013</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>35810040</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>35810040.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>36.87</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>40.07</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>40.07</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>39561838.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>77102277.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>77102277.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>54515793.2</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>33864219.92</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>33864219.92</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>11730479.54280426</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>39561838</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>39561838.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>36.60000000000001</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>38.22</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>40.17</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>40.17</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>232650449.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>74142370.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>74142370</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>57245793.0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>34130931.06</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>34130931.06</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>16400757.27416717</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>232650449</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>36.61</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>40.3</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>41298962.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>35487232.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>35487232</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>35914543.8</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>29950115.64</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>29950115.64</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>1798775.809179619</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>41298962</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>41298962.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>40.43</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>40.43</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>28176624.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>37871124.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>37871124</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>34509118.0</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>29545425.32</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>29545425.32</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>1376505.330298137</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>28176624</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>28176624.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>37.07000000000001</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>40.58</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>40.58</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>43823516.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>36085517.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>36085517.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>35025550.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>29409986.0</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>29409986</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>2130065.670099653</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>43823516</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>43823516.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>37.47000000000001</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>40.75</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>40.75</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>24762299.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>31929308.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>31929308.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>32595150.7</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>29130934.74</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>29130934.74</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>1454053.953026839</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>24762299</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>24762299.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>37.65000000000001</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>39.23</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>39374759.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>40349216.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>40349216</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>31454761.9</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>29061426.18</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>29061426.18</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>2478665.680314712</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>39374759</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>39374759.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>37.99</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>39.42</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>41.05</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>41.05</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>53218422.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>36341855.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>36341855.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>29562657.9</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>28846965.04</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>28846965.04</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>2288252.230714723</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>53218422</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>53218422.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>38.31</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>39.58</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>19248593.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>31147112.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>31147112</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>25871081.1</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>28091032.78</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>28091032.78</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>451260.1159035005</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>19248593</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>19248593.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>38.46</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>39.69</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>41.29</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>41.29</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>23042470.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>33965584.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>33965584</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>26178217.9</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>28206383.42</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>28206383.42</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>1450493.769176625</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>23042470</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>23042470.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>15.16</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>15.42</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>16.16</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>16.16</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>759015.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>822662.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>822662.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>899025.8</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>839437.72</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>839437.72</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-27651.22974182363</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>759015</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>759015.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>15.09</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>16.2</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>610121.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>888460.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>888460.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>911030.7</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>833228.32</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>833228.3199999999</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-24939.23107736837</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>610121</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>610121.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>15.14</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>16.25</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>328107.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1019582.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1019582.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>881008.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>833631.48</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>833631.48</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-4221.331875383272</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>328107</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>328107.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>15.21</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>15.53</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>16.3</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1370613.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1039667.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1039667.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>976340.4</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>832143.12</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>832143.12</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>55742.21455157339</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1370613</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1370613.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>15.29</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>16.35</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>16.35</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>1045458.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>969620.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>969620.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>895996.7</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>815201.94</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>815201.9399999999</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>27716.55892752646</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>1045458</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>1045458.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>15.34</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>16.4</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>1088003.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>975388.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>975388.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>889500.6</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>803125.26</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>803125.26</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>21528.0666457623</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>1088003</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>1088003.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>15.38</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>15.64</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>16.45</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>16.45</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>1265731.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>933601.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>933601</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>848828.0</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>789392.84</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>789392.84</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>7360.111005893559</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>1265731</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>1265731.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>15.4</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>16.49</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>16.49</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>428532.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>742433.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>742433.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>764703.6</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>770458.0</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>770458</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-32184.97244412953</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>428532</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>428532.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>15.43</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>15.7</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>16.53</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>16.53</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>1020378.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>913013.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>913013.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>789901.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>831542.84</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>831542.84</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>2171.407357413555</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>1020378</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>1020378.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>15.47</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>15.75</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>16.58</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>16.58</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>1074300.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>822373.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>822373</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>741812.3</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>839169.14</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>839169.14</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-12237.67176028958</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>1074300</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>1074300.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>15.51</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>15.8</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>16.62</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>16.62</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>879064.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>803612.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>803612.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>728036.7</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>823720.16</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>823720.16</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-38162.36793699802</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>879064</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>879064.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>17.25</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>18.16</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>13613928.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>10372257.8</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>10372257.8</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>15735161.0</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>35709154.84</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>35709154.84</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-2546499.088265551</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>13613928</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>13613928.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>17.08</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>18.26</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>20.36</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>20.36</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>8481553.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>10158688.6</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>10158688.6</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>15635933.7</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>36006631.54</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>36006631.54</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-2868767.912395775</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>8481553</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>8481553.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>17.13</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>18.41</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>20.43</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>11267596.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>15708299.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>15708299.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>16935768.7</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>36089158.58</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>36089158.58</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-2676798.628567677</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>11267596</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>11267596.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>17.24</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>18.57</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>20.5</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>13526868.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>15807963.6</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>15807963.6</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>17674597.8</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>36309850.68</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>36309850.68</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-2605461.450650116</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>13526868</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>13526868.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>17.44</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>18.77</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>20.58</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>20.58</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>4971344.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>18192489.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>18192489.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>17817474.1</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>36286025.3</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>36286025.3</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-2652563.858958956</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>4971344</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>4971344.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>17.64</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>20.66</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>20.66</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>12546082.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>21098064.2</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>21098064.2</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>19015490.5</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>36438805.22</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>36438805.22</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-1708455.304437336</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>12546082</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>12546082.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>17.93</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>20.75</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>20.75</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>36229606.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>21113178.8</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>21113178.8</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>19952648.9</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>36367077.28</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>36367077.28</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-1110291.608533688</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>36229606</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>36229606.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>18.08</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>19.51</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>20.83</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>20.83</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>11765918.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>18163238.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>18163238.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>18465394.1</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>35922851.76</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>35922851.76</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-2753639.199795127</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>11765918</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>11765918.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>18.21</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>20.91</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>20.91</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>25449498.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>19541232.0</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>19541232</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>19684784.3</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>35922462.82</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>35922462.82</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-2381824.930175934</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>25449498</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>25449498.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>18.34</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>21</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>19499217.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>17442458.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>17442458.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>18972660.0</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>35662849.28</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>35662849.28</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-3231694.368927941</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>19499217</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>19499217.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>18.42</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>20.21</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>21.07</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>21.07</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>12621655.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>16932916.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>16932916.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>19086589.9</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>35528913.86</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>35528913.86</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-3692845.803969096</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>12621655</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>12621655.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
